--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_DUBAI BASKETBALL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_DUBAI BASKETBALL.xlsx
@@ -565,13 +565,13 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>82.79260000000001</v>
+        <v>55.2991</v>
       </c>
       <c r="E2" t="n">
-        <v>67.5741</v>
+        <v>46.5034</v>
       </c>
       <c r="F2" t="n">
-        <v>15.2185</v>
+        <v>8.795400000000001</v>
       </c>
       <c r="G2" t="n">
         <v>10.1933</v>
@@ -610,13 +610,13 @@
         <v>47.5508</v>
       </c>
       <c r="S2" t="n">
-        <v>44.5597</v>
+        <v>17.0662</v>
       </c>
       <c r="T2" t="n">
-        <v>28.2671</v>
+        <v>7.1964</v>
       </c>
       <c r="U2" t="n">
-        <v>16.2932</v>
+        <v>9.870100000000001</v>
       </c>
       <c r="V2" t="n">
         <v>25.0239</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>42.9127</v>
+        <v>47.4507</v>
       </c>
       <c r="E3" t="n">
-        <v>44.7741</v>
+        <v>58.8936</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8614</v>
+        <v>-11.4424</v>
       </c>
       <c r="G3" t="n">
-        <v>-13.992</v>
+        <v>59.5683</v>
       </c>
       <c r="H3" t="n">
-        <v>2.145700000000001</v>
+        <v>39.2289</v>
       </c>
       <c r="I3" t="n">
-        <v>-16.1377</v>
+        <v>20.3388</v>
       </c>
       <c r="J3" t="n">
-        <v>30.2085</v>
+        <v>105.3837</v>
       </c>
       <c r="K3" t="n">
-        <v>17.8893</v>
+        <v>51.2365</v>
       </c>
       <c r="L3" t="n">
-        <v>12.3187</v>
+        <v>54.1477</v>
       </c>
       <c r="M3" t="n">
-        <v>-44.2003</v>
+        <v>-45.8156</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.7442</v>
+        <v>-12.0072</v>
       </c>
       <c r="O3" t="n">
-        <v>-28.4563</v>
+        <v>-33.8086</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2476</v>
+        <v>-24.8187</v>
       </c>
       <c r="Q3" t="n">
-        <v>-52.1898</v>
+        <v>-92.3172</v>
       </c>
       <c r="R3" t="n">
-        <v>55.4369</v>
+        <v>67.4984</v>
       </c>
       <c r="S3" t="n">
-        <v>16.4318</v>
+        <v>-2.1362</v>
       </c>
       <c r="T3" t="n">
-        <v>4.854900000000001</v>
+        <v>-5.6529</v>
       </c>
       <c r="U3" t="n">
-        <v>11.5769</v>
+        <v>3.5163</v>
       </c>
       <c r="V3" t="n">
-        <v>37.2259</v>
+        <v>14.8379</v>
       </c>
       <c r="W3" t="n">
-        <v>61.9002</v>
+        <v>51.4793</v>
       </c>
       <c r="X3" t="n">
-        <v>-24.6743</v>
+        <v>-36.6414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>15.7208</v>
+        <v>35.681</v>
       </c>
       <c r="E4" t="n">
-        <v>38.4885</v>
+        <v>41.3882</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.7675</v>
+        <v>-5.707599999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>59.5683</v>
+        <v>-13.992</v>
       </c>
       <c r="H4" t="n">
-        <v>39.2289</v>
+        <v>2.145700000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>20.3388</v>
+        <v>-16.1377</v>
       </c>
       <c r="J4" t="n">
-        <v>105.3837</v>
+        <v>30.2085</v>
       </c>
       <c r="K4" t="n">
-        <v>51.2365</v>
+        <v>17.8893</v>
       </c>
       <c r="L4" t="n">
-        <v>54.1477</v>
+        <v>12.3187</v>
       </c>
       <c r="M4" t="n">
-        <v>-45.8156</v>
+        <v>-44.2003</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.0072</v>
+        <v>-15.7442</v>
       </c>
       <c r="O4" t="n">
-        <v>-33.8086</v>
+        <v>-28.4563</v>
       </c>
       <c r="P4" t="n">
-        <v>-24.8187</v>
+        <v>3.2476</v>
       </c>
       <c r="Q4" t="n">
-        <v>-92.3172</v>
+        <v>-52.1898</v>
       </c>
       <c r="R4" t="n">
-        <v>67.4984</v>
+        <v>55.4369</v>
       </c>
       <c r="S4" t="n">
-        <v>-33.8664</v>
+        <v>9.1997</v>
       </c>
       <c r="T4" t="n">
-        <v>-26.058</v>
+        <v>1.469</v>
       </c>
       <c r="U4" t="n">
-        <v>-7.808800000000001</v>
+        <v>7.7303</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8379</v>
+        <v>37.2259</v>
       </c>
       <c r="W4" t="n">
-        <v>51.4793</v>
+        <v>61.9002</v>
       </c>
       <c r="X4" t="n">
-        <v>-36.6414</v>
+        <v>-24.6743</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>7.848</v>
+        <v>9.139699999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>17.7158</v>
+        <v>16.5518</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.867599999999999</v>
+        <v>-7.4119</v>
       </c>
       <c r="G5" t="n">
         <v>-4.108600000000002</v>
@@ -844,13 +844,13 @@
         <v>29.2262</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.3486</v>
+        <v>-4.0563</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4030999999999999</v>
+        <v>-0.7608000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.7514</v>
+        <v>-3.2956</v>
       </c>
       <c r="V5" t="n">
         <v>23.3359</v>
@@ -877,13 +877,13 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>5.2536</v>
+        <v>1.1781</v>
       </c>
       <c r="E6" t="n">
-        <v>18.7006</v>
+        <v>15.3863</v>
       </c>
       <c r="F6" t="n">
-        <v>-13.4471</v>
+        <v>-14.2079</v>
       </c>
       <c r="G6" t="n">
         <v>12.7736</v>
@@ -922,13 +922,13 @@
         <v>9.0464</v>
       </c>
       <c r="S6" t="n">
-        <v>3.576</v>
+        <v>-0.4994999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1969</v>
+        <v>0.8824000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6211</v>
+        <v>-1.3819</v>
       </c>
       <c r="V6" t="n">
         <v>-14.1114</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>B. ELLIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.282099999999998</v>
+        <v>1.1191</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0882</v>
+        <v>6.0778</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.805800000000001</v>
+        <v>-4.9586</v>
       </c>
       <c r="G7" t="n">
-        <v>-12.45</v>
+        <v>-3.7827</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.980199999999999</v>
+        <v>-2.4444</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.4701</v>
+        <v>-1.3384</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5403</v>
+        <v>2.1296</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3408999999999995</v>
+        <v>0.1393000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>5.1994</v>
+        <v>1.9904</v>
       </c>
       <c r="M7" t="n">
-        <v>-17.9903</v>
+        <v>-5.9123</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.3202</v>
+        <v>-2.5836</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.6694</v>
+        <v>-3.3288</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.4792</v>
+        <v>3.4793</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.6441</v>
+        <v>-3.4794</v>
       </c>
       <c r="R7" t="n">
-        <v>17.1649</v>
+        <v>6.9586</v>
       </c>
       <c r="S7" t="n">
-        <v>23.2582</v>
+        <v>-1.0053</v>
       </c>
       <c r="T7" t="n">
-        <v>16.5213</v>
+        <v>-0.1089</v>
       </c>
       <c r="U7" t="n">
-        <v>6.7372</v>
+        <v>-0.8964</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.0463</v>
+        <v>2.428</v>
       </c>
       <c r="W7" t="n">
-        <v>8.6709</v>
+        <v>7.5364</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.7172</v>
+        <v>-5.1085</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1207</v>
+        <v>0.5288999999999997</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7225000000000001</v>
+        <v>1.1077</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6016999999999999</v>
+        <v>-0.5789000000000002</v>
       </c>
       <c r="G8" t="n">
         <v>1.7365</v>
@@ -1078,13 +1078,13 @@
         <v>4.1753</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4225</v>
+        <v>-1.0142</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2784000000000001</v>
+        <v>0.1067999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1439</v>
+        <v>-1.1211</v>
       </c>
       <c r="V8" t="n">
         <v>-0.4254000000000001</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. ELLIS</t>
+          <t>D. ANDJUSIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.01359999999999983</v>
+        <v>-0.0689</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3819</v>
+        <v>-0.7992</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.3955</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7827</v>
+        <v>-1.5943</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4444</v>
+        <v>-0.3361</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3384</v>
+        <v>-1.2582</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1296</v>
+        <v>-1.5727</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1393000000000001</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9904</v>
+        <v>-1.5727</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.9123</v>
+        <v>-0.0216</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5836</v>
+        <v>-0.3361</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.3288</v>
+        <v>0.3145</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4793</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4794</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6.9586</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1381</v>
+        <v>-0.2427</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8048000000000001</v>
+        <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3333</v>
+        <v>0.056</v>
       </c>
       <c r="V9" t="n">
-        <v>2.428</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>7.5364</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.1085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ANDJUSIC</t>
+          <t>A. AVRAMOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1025</v>
+        <v>-1.6752</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7992</v>
+        <v>1.063600000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6967</v>
+        <v>-2.7391</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5943</v>
+        <v>2.819500000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3361</v>
+        <v>3.8453</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2582</v>
+        <v>-1.0256</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5727</v>
+        <v>20.298</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>12.9471</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5727</v>
+        <v>7.3509</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0216</v>
+        <v>-17.4783</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3361</v>
+        <v>-9.102</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3145</v>
+        <v>-8.3764</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-8.5822</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-34.7929</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>26.2109</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2763</v>
+        <v>-5.1991</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>-1.548</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0224</v>
+        <v>-3.6508</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>9.2866</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>17.1067</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-7.8201</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. RYAN</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9233</v>
+        <v>-1.697299999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4806</v>
+        <v>-2.940000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4427</v>
+        <v>1.2427</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6873</v>
+        <v>4.8328</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1379</v>
+        <v>4.4984</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5494</v>
+        <v>0.3343000000000007</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2753</v>
+        <v>12.5385</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5881999999999999</v>
+        <v>10.289</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8633999999999999</v>
+        <v>2.249900000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4119</v>
+        <v>-7.7058</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7261</v>
+        <v>-5.790500000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6858</v>
+        <v>-1.9155</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8556</v>
+        <v>-3.9434</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-24.8194</v>
       </c>
       <c r="R11" t="n">
-        <v>0.464</v>
+        <v>20.8761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3805</v>
+        <v>-0.6637000000000002</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1142</v>
+        <v>-2.3742</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4946</v>
+        <v>1.7105</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.923</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>11.7146</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-13.6376</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.439</v>
+        <v>-2.6511</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8278</v>
+        <v>8.910100000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6112</v>
+        <v>-11.5614</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.727400000000001</v>
+        <v>-8.1541</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.287800000000001</v>
+        <v>-0.5026000000000004</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4397</v>
+        <v>-7.651899999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5367</v>
+        <v>26.3206</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0105</v>
+        <v>11.4878</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5258</v>
+        <v>14.8328</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.191</v>
+        <v>-34.475</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.2772</v>
+        <v>-11.9907</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9138</v>
+        <v>-22.4849</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6393</v>
+        <v>23.6593</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7836</v>
+        <v>-25.9791</v>
       </c>
       <c r="R12" t="n">
-        <v>7.4227</v>
+        <v>49.638</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0799</v>
+        <v>-2.2944</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7446</v>
+        <v>-4.8658</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6647</v>
+        <v>2.5714</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.4306</v>
+        <v>-15.8616</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2524999999999999</v>
+        <v>13.4336</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1781</v>
+        <v>-29.2951</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. ARMSTRONG</t>
+          <t>M. RYAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.476699999999999</v>
+        <v>-3.6823</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9453</v>
+        <v>-2.5985</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5314</v>
+        <v>-1.0838</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2714</v>
+        <v>-1.6873</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5715999999999999</v>
+        <v>-0.1379</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8431000000000001</v>
+        <v>-1.5494</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4441000000000001</v>
+        <v>-0.2753</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2806</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8365</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7153999999999999</v>
+        <v>-1.4119</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7090000000000001</v>
+        <v>-0.7261</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.006499999999999957</v>
+        <v>-0.6858</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5514</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.6391</v>
+        <v>-2.3195</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0877</v>
+        <v>0.464</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9422</v>
+        <v>-0.1395</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7503</v>
+        <v>-0.003799999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.192</v>
+        <v>-0.1357</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7116</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.812899999999999</v>
+        <v>-4.058400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9388000000000001</v>
+        <v>0.5706999999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.874</v>
+        <v>-4.6293</v>
       </c>
       <c r="G14" t="n">
         <v>-4.5732</v>
@@ -1546,13 +1546,13 @@
         <v>12.5257</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.2033</v>
+        <v>-3.449</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.1665</v>
+        <v>-1.6569</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.0369</v>
+        <v>-1.7921</v>
       </c>
       <c r="V14" t="n">
         <v>0.2525000000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. AVRAMOVIC</t>
+          <t>T. ARMSTRONG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.970000000000002</v>
+        <v>-5.4095</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.1678</v>
+        <v>-4.0017</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.802299999999999</v>
+        <v>-1.4078</v>
       </c>
       <c r="G15" t="n">
-        <v>2.819500000000001</v>
+        <v>-0.2714</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8453</v>
+        <v>0.5715999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0256</v>
+        <v>-0.8431000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>20.298</v>
+        <v>0.4441000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>12.9471</v>
+        <v>1.2806</v>
       </c>
       <c r="L15" t="n">
-        <v>7.3509</v>
+        <v>-0.8365</v>
       </c>
       <c r="M15" t="n">
-        <v>-17.4783</v>
+        <v>-0.7153999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.102</v>
+        <v>-0.7090000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.3764</v>
+        <v>-0.006499999999999957</v>
       </c>
       <c r="P15" t="n">
-        <v>-8.5822</v>
+        <v>-2.5514</v>
       </c>
       <c r="Q15" t="n">
-        <v>-34.7929</v>
+        <v>-4.6391</v>
       </c>
       <c r="R15" t="n">
-        <v>26.2109</v>
+        <v>2.0877</v>
       </c>
       <c r="S15" t="n">
-        <v>-10.4941</v>
+        <v>0.125</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.7797</v>
+        <v>0.1933</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.7142</v>
+        <v>-0.06829999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>9.2866</v>
+        <v>-2.7116</v>
       </c>
       <c r="W15" t="n">
-        <v>17.1067</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.8201</v>
+        <v>-2.7116</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.6823</v>
+        <v>-8.4314</v>
       </c>
       <c r="E16" t="n">
-        <v>4.715399999999999</v>
+        <v>-4.607699999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-15.3974</v>
+        <v>-3.8236</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.1541</v>
+        <v>-8.727400000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5026000000000004</v>
+        <v>-4.287800000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.651899999999999</v>
+        <v>-4.4397</v>
       </c>
       <c r="J16" t="n">
-        <v>26.3206</v>
+        <v>-2.5367</v>
       </c>
       <c r="K16" t="n">
-        <v>11.4878</v>
+        <v>-1.0105</v>
       </c>
       <c r="L16" t="n">
-        <v>14.8328</v>
+        <v>-1.5258</v>
       </c>
       <c r="M16" t="n">
-        <v>-34.475</v>
+        <v>-6.191</v>
       </c>
       <c r="N16" t="n">
-        <v>-11.9907</v>
+        <v>-3.2772</v>
       </c>
       <c r="O16" t="n">
-        <v>-22.4849</v>
+        <v>-2.9138</v>
       </c>
       <c r="P16" t="n">
-        <v>23.6593</v>
+        <v>4.6393</v>
       </c>
       <c r="Q16" t="n">
-        <v>-25.9791</v>
+        <v>-2.7836</v>
       </c>
       <c r="R16" t="n">
-        <v>49.638</v>
+        <v>7.4227</v>
       </c>
       <c r="S16" t="n">
-        <v>-10.3255</v>
+        <v>0.08739999999999992</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.0601</v>
+        <v>0.9647</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2649</v>
+        <v>-0.8771</v>
       </c>
       <c r="V16" t="n">
-        <v>-15.8616</v>
+        <v>-4.4306</v>
       </c>
       <c r="W16" t="n">
-        <v>13.4336</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-29.2951</v>
+        <v>-4.1781</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.1174</v>
+        <v>-8.904499999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.851900000000001</v>
+        <v>-2.2215</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2655</v>
+        <v>-6.6831</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8328</v>
+        <v>-19.9349</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4984</v>
+        <v>-4.8354</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3343000000000007</v>
+        <v>-15.0996</v>
       </c>
       <c r="J17" t="n">
-        <v>12.5385</v>
+        <v>5.6279</v>
       </c>
       <c r="K17" t="n">
-        <v>10.289</v>
+        <v>5.9109</v>
       </c>
       <c r="L17" t="n">
-        <v>2.249900000000001</v>
+        <v>-0.2825</v>
       </c>
       <c r="M17" t="n">
-        <v>-7.7058</v>
+        <v>-25.563</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.790500000000001</v>
+        <v>-10.7461</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9155</v>
+        <v>-14.8165</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.9434</v>
+        <v>20.4122</v>
       </c>
       <c r="Q17" t="n">
-        <v>-24.8194</v>
+        <v>-11.1341</v>
       </c>
       <c r="R17" t="n">
-        <v>20.8761</v>
+        <v>31.5462</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.0841</v>
+        <v>-0.2364000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.286300000000001</v>
+        <v>0.4306999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.798</v>
+        <v>-0.6673</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.923</v>
+        <v>-9.1448</v>
       </c>
       <c r="W17" t="n">
-        <v>11.7146</v>
+        <v>2.8534</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.6376</v>
+        <v>-11.9982</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.038</v>
+        <v>-13.6079</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.595999999999999</v>
+        <v>-1.569599999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.4418</v>
+        <v>-12.0384</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.9349</v>
+        <v>-12.45</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.8354</v>
+        <v>-4.980199999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-15.0996</v>
+        <v>-7.4701</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6279</v>
+        <v>5.5403</v>
       </c>
       <c r="K18" t="n">
-        <v>5.9109</v>
+        <v>0.3408999999999995</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2825</v>
+        <v>5.1994</v>
       </c>
       <c r="M18" t="n">
-        <v>-25.563</v>
+        <v>-17.9903</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.7461</v>
+        <v>-5.3202</v>
       </c>
       <c r="O18" t="n">
-        <v>-14.8165</v>
+        <v>-12.6694</v>
       </c>
       <c r="P18" t="n">
-        <v>20.4122</v>
+        <v>-3.4792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-11.1341</v>
+        <v>-20.6441</v>
       </c>
       <c r="R18" t="n">
-        <v>31.5462</v>
+        <v>17.1649</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.369999999999999</v>
+        <v>7.3673</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.9433</v>
+        <v>4.8636</v>
       </c>
       <c r="U18" t="n">
-        <v>-7.4262</v>
+        <v>2.5041</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.1448</v>
+        <v>-5.0463</v>
       </c>
       <c r="W18" t="n">
-        <v>2.8534</v>
+        <v>8.6709</v>
       </c>
       <c r="X18" t="n">
-        <v>-11.9982</v>
+        <v>-13.7172</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>-30.6377</v>
+        <v>-15.8832</v>
       </c>
       <c r="E19" t="n">
-        <v>-43.867</v>
+        <v>-31.0694</v>
       </c>
       <c r="F19" t="n">
-        <v>13.2295</v>
+        <v>15.1865</v>
       </c>
       <c r="G19" t="n">
         <v>-21.301</v>
@@ -1936,13 +1936,13 @@
         <v>49.6381</v>
       </c>
       <c r="S19" t="n">
-        <v>-15.8984</v>
+        <v>-1.1437</v>
       </c>
       <c r="T19" t="n">
-        <v>-16.5775</v>
+        <v>-3.7801</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6792999999999997</v>
+        <v>2.6365</v>
       </c>
       <c r="V19" t="n">
         <v>35.5554</v>
@@ -1969,13 +1969,13 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>-34.7199</v>
+        <v>-25.2942</v>
       </c>
       <c r="E20" t="n">
-        <v>-21.2803</v>
+        <v>-14.4352</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.4399</v>
+        <v>-10.8588</v>
       </c>
       <c r="G20" t="n">
         <v>-25.1236</v>
@@ -2014,13 +2014,13 @@
         <v>33.8655</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.7238</v>
+        <v>-2.2984</v>
       </c>
       <c r="T20" t="n">
-        <v>-9.770900000000001</v>
+        <v>-2.926200000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.953</v>
+        <v>0.6277000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-13.1811</v>
@@ -2047,22 +2047,22 @@
         <v>38</v>
       </c>
       <c r="D21" t="n">
-        <v>20.99720000000003</v>
+        <v>59.03269999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>115.4064</v>
+        <v>132.2104</v>
       </c>
       <c r="F21" t="n">
-        <v>-94.40809999999999</v>
+        <v>-73.17769999999997</v>
       </c>
       <c r="G21" t="n">
         <v>-33.7765</v>
       </c>
       <c r="H21" t="n">
-        <v>50.6709</v>
+        <v>50.67089999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-84.44949999999999</v>
+        <v>-84.4495</v>
       </c>
       <c r="J21" t="n">
         <v>287.1882</v>
@@ -2083,22 +2083,22 @@
         <v>-201.2213</v>
       </c>
       <c r="P21" t="n">
-        <v>1.161799999999998</v>
+        <v>1.161799999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-470.8676</v>
+        <v>-470.8675999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>472.0283000000001</v>
+        <v>472.0283</v>
       </c>
       <c r="S21" t="n">
-        <v>-28.5682</v>
+        <v>9.467199999999998</v>
       </c>
       <c r="T21" t="n">
-        <v>-24.6724</v>
+        <v>-7.869400000000002</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.894000000000003</v>
+        <v>17.3366</v>
       </c>
       <c r="V21" t="n">
         <v>82.18249999999999</v>
